--- a/scenarios/07_karen_test_engineer/7.1_nedt_reconciliation/outputs/nedt_reconciliation_results.xlsx
+++ b/scenarios/07_karen_test_engineer/7.1_nedt_reconciliation/outputs/nedt_reconciliation_results.xlsx
@@ -523,10 +523,10 @@
         <v>160</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>138.7</v>
+        <v>124.66</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>21.3</v>
+        <v>35.34</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>97857</v>
@@ -535,10 +535,10 @@
         <v>3758.9</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>521.36</v>
+        <v>468.59</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>187.7</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="5">
@@ -552,10 +552,10 @@
         <v>142</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>123.04</v>
+        <v>111.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>18.96</v>
+        <v>30.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>118204</v>
@@ -564,10 +564,10 @@
         <v>4392.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>540.52</v>
+        <v>489.82</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>218.7</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="6">
@@ -581,10 +581,10 @@
         <v>127</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>110.08</v>
+        <v>100.57</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>16.92</v>
+        <v>26.43</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>141916</v>
@@ -593,10 +593,10 @@
         <v>5105.7</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>562.03</v>
+        <v>513.46</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>252.5</v>
+        <v>276.4</v>
       </c>
     </row>
     <row r="7">
@@ -610,10 +610,10 @@
         <v>114</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>99.27</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.73</v>
+        <v>22.6</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>169401</v>
@@ -622,10 +622,10 @@
         <v>5903</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>585.97</v>
+        <v>539.5599999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>289.1</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
@@ -639,10 +639,10 @@
         <v>104</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>90.18000000000001</v>
+        <v>83.67</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.82</v>
+        <v>20.33</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>201096</v>
@@ -651,10 +651,10 @@
         <v>6790.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>612.42</v>
+        <v>568.17</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>328.4</v>
+        <v>353.9</v>
       </c>
     </row>
     <row r="9">
@@ -668,10 +668,10 @@
         <v>95</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>82.5</v>
+        <v>77.08</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.5</v>
+        <v>17.92</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>237468</v>
@@ -680,10 +680,10 @@
         <v>7775.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>641.4299999999999</v>
+        <v>599.3200000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>370.2</v>
+        <v>396.2</v>
       </c>
     </row>
     <row r="10">
@@ -697,10 +697,10 @@
         <v>81</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>70.33</v>
+        <v>66.55</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.67</v>
+        <v>14.45</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>326266</v>
@@ -709,10 +709,10 @@
         <v>10056.9</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>707.27</v>
+        <v>669.3200000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>461.3</v>
+        <v>487.5</v>
       </c>
     </row>
   </sheetData>
@@ -777,7 +777,7 @@
         <v>73.78400000000001</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="5">
@@ -793,52 +793,52 @@
         <v>68.27200000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38.5</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>nearfield_shot</t>
+          <t>read_noise</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>228.56</v>
+        <v>14.2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>44.766</v>
+        <v>2.781</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>16.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>read_noise</t>
+          <t>quantization</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>14.2</v>
+        <v>3.46</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.781</v>
+        <v>0.678</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>quantization</t>
+          <t>dark_shot</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3.46</v>
+        <v>0.26</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.678</v>
+        <v>0.051</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -847,14 +847,14 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>dark_shot</t>
+          <t>nearfield_shot</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110.634</v>
+        <v>101.072</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>109.532</v>
+        <v>100.066</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.5508</v>
+        <v>-0.5033</v>
       </c>
     </row>
     <row r="5">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>110.079</v>
+        <v>100.565</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>110.079</v>
+        <v>100.565</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -1144,13 +1144,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>110.078</v>
+        <v>100.564</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>110.08</v>
+        <v>100.566</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="7">
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>110.634</v>
+        <v>101.072</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>109.532</v>
+        <v>100.066</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-0.5508</v>
+        <v>-0.5033</v>
       </c>
     </row>
     <row r="8">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>110.952</v>
+        <v>101.072</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>109.223</v>
+        <v>100.066</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0.8647</v>
+        <v>-0.5033</v>
       </c>
     </row>
     <row r="9">
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>108.977</v>
+        <v>99.559</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>111.18</v>
+        <v>101.572</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.1015</v>
+        <v>1.0065</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110.08</t>
+          <t>100.57</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>103.37</t>
+          <t>95.18</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>26.43</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>562.03</t>
+          <t>513.46</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>276.4</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>323.38</t>
+          <t>396.00</t>
         </is>
       </c>
     </row>
